--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -1,98 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/taeyoonkwack/Documents/Isaac_franka_conveyor/results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4574DFA3-99FC-A747-8C83-291C7DB48086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="12220" yWindow="3100" windowWidth="35820" windowHeight="16680" xr2:uid="{15E77579-56ED-8640-A6B5-1E174931DEA0}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12220" yWindow="3100" windowWidth="35820" windowHeight="16680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
-  <si>
-    <t>Task2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Task1</t>
-  </si>
-  <si>
-    <t>Task3</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>Safe</t>
-  </si>
-  <si>
-    <t>LC + Ours</t>
-  </si>
-  <si>
-    <t>LC</t>
-  </si>
-  <si>
-    <t>VLS</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
-    <t>SC + Ours</t>
-  </si>
-  <si>
-    <t>VLS + Ours</t>
-  </si>
-  <si>
-    <t>N=50</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -227,67 +162,128 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -607,122 +603,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC614DA3-99A2-1943-9352-67E571771FFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="1"/>
+    <col width="21" customWidth="1" style="1" min="1" max="1"/>
+    <col width="10.83203125" customWidth="1" style="1" min="2" max="3"/>
+    <col width="10.83203125" customWidth="1" style="1" min="4" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>N=50</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Task1</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="n"/>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Task2</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="n"/>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Task3</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n"/>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>SR</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>LC + Ours</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="15" t="s">
+      <c r="C5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="14"/>
+      <c r="D5" s="15" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="12"/>
-      <c r="B2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>4</v>
-      </c>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>SC + Ours</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="9" t="n"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="4"/>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>VLS</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="n"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="9"/>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>VLS + Ours</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -675,104 +675,111 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>LC</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B4" s="13" t="n">
         <v>0.96</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.04</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D4" s="15" t="n">
         <v>0.42</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E4" s="15" t="n">
         <v>0.32</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F4" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G4" s="14" t="n">
         <v>0.76</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>LC + Ours</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="9" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C6" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D6" s="15" t="n">
         <v>0.96</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E6" s="15" t="n">
         <v>0.54</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F6" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G6" s="14" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>SC + Ours</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>VLS</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>VLS + Ours</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="9" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -680,6 +680,24 @@
           <t>VLA</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -763,10 +781,24 @@
           <t>VLS</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="B8" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -693,10 +693,10 @@
         <v>0.04</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="G3" t="n">
-        <v>0.92</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="4">
@@ -718,10 +718,10 @@
         <v>0.32</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0.76</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5">
@@ -756,10 +756,10 @@
         <v>0.54</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -624,22 +624,21 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Task1</t>
-        </is>
-      </c>
-      <c r="C1" s="16" t="n"/>
-      <c r="D1" s="15" t="inlineStr">
+          <t>Task1</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="n"/>
+      <c r="D1" s="16" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Task2</t>
         </is>
       </c>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Task3</t>
         </is>
       </c>
-      <c r="G1" s="16" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n"/>
@@ -655,22 +654,37 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
           <t>SR</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Help</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>SR</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Safe</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Help</t>
         </is>
       </c>
     </row>
@@ -687,16 +701,25 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.66</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.04</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.62</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.08</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -712,16 +735,25 @@
         <v>0.04</v>
       </c>
       <c r="D4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15" t="n">
         <v>0.42</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="F4" s="13" t="n">
         <v>0.32</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="G4" s="14" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.34</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="I4" t="n">
         <v>0.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -750,16 +782,25 @@
         <v>0</v>
       </c>
       <c r="D6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
         <v>0.96</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="F6" s="13" t="n">
         <v>0.54</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" s="14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -788,16 +829,25 @@
         <v>0.08</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.76</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.36</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -815,9 +865,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -835,39 +835,73 @@
         <v>0.76</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VLS_authentic</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>VLS + Ours</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="21" customWidth="1" style="1" min="1" max="1"/>
@@ -851,57 +851,23 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VLS_authentic</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>VLS + Ours</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -762,12 +762,33 @@
           <t>LC + Ours</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="9" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -809,12 +830,33 @@
           <t>SC + Ours</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -856,18 +898,39 @@
           <t>VLS + Ours</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="B9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/industry_results.xlsx
+++ b/results/industry_results.xlsx
@@ -766,28 +766,28 @@
         <v>0.92</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="6">
@@ -840,22 +840,22 @@
         <v>1</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="H7" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="8">
@@ -908,22 +908,22 @@
         <v>1</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
